--- a/Hoadon/HDRa/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/11/HDDienTuMayTinhTien.xlsx
@@ -308,57 +308,61 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>865</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>3502264227</t>
+          <t>0202285936</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>Trường Tiểu Học Võ Văn Kiệt</t>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN ­ - TỔNG CÔNG TY BẢO ĐẢM AN TOÀN HÀNG HẢI VIỆT NAM</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Ấp Phước Thắng, Xã Long Hải, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 1 lô 11A đường Lê Hồng Phong,Phường Hải An,Thành phố Hải Phòng,Việt Nam</t>
         </is>
       </c>
       <c r="K7" s="6"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
+      <c r="L7" s="13" t="n">
+        <v>926186.0</v>
+      </c>
+      <c r="M7" s="13" t="n">
+        <v>74095.0</v>
+      </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>2600000.0</v>
+        <v>1000281.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -377,57 +381,61 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>866</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>3502222883</t>
+          <t>0100111948-043</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH ĐẦU TƯ XÂY DỰNG-THƯƠNG MẠI HOÀNG GIA</t>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN CÔNG THƯƠNG VIỆT NAM - CHI NHÁNH BÀ RỊA-VŨNG TÀU</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Số 32 Huỳnh Khương An, Phường Bà Rịa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 10 Trưng Trắc, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K8" s="6"/>
-      <c r="L8" s="13"/>
-      <c r="M8" s="13"/>
+      <c r="L8" s="13" t="n">
+        <v>4537816.0</v>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>363025.0</v>
+      </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>3800000.0</v>
+        <v>4900841.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -446,57 +454,61 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>867</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>3502441846</t>
+          <t>3500673707</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>Công ty cổ phần BTT Tech</t>
+          <t>CÔNG TY CỔ PHẦN DƯỢC PHẨM VÀ TRANG THIẾT BỊ Y TẾ VĨNH KHANG</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Đường số 6 Khu công nghiệp Đông Xuyên, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam.</t>
+          <t>Nhà số 30 Khu nhà ở Phước Sơn (Đường 11), đường 2/9, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K9" s="6"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
+      <c r="L9" s="13" t="n">
+        <v>560000.0</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>56000.0</v>
+      </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>6510000.0</v>
+        <v>616000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -515,57 +527,61 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>868</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>06/11/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>0100109106-122</t>
+          <t>3500673707</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>VIETTEL THÀNH PHỐ HỒ CHÍ MINH - CHI NHÁNH TẬP ĐOÀN CÔNG NGHIỆP - VIỄN THÔNG QUÂN ĐỘI</t>
+          <t>CÔNG TY CỔ PHẦN DƯỢC PHẨM VÀ TRANG THIẾT BỊ Y TẾ VĨNH KHANG</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>285 Đường Cách Mạng Tháng Tám, Phường Hòa Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Nhà số 30 Khu nhà ở Phước Sơn (Đường 11), đường 2/9, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K10" s="6"/>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
+      <c r="L10" s="13" t="n">
+        <v>667940.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>53435.0</v>
+      </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>800000.0</v>
+        <v>721375.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -584,57 +600,61 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>869</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>3500660200</t>
+          <t>0100931299-010</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ VÀ XÂY DỰNG TÂN PHƯỚC THỊNH</t>
+          <t>CÔNG TY BẢO HIỂM BIDV VŨNG TÀU</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Số 71 đường 3/2, Phường Tam Thắng ,Thành phố Hồ Chí Minh, Việt Nam</t>
+          <t>24 Trần Hưng Đạo, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K11" s="6"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
+      <c r="L11" s="13" t="n">
+        <v>1853700.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>148296.0</v>
+      </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>780000.0</v>
+        <v>2001996.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -653,57 +673,61 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MDV</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>870</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>07/11/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>077091004164</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>HỘ KINH DOANH NGUYỄN ĐỨC VŨ</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>0100109106-122</t>
+          <t>0102737963-033</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>VIETTEL THÀNH PHỐ HỒ CHÍ MINH - CHI NHÁNH TẬP ĐOÀN CÔNG NGHIỆP - VIỄN THÔNG QUÂN ĐỘI</t>
+          <t>CÔNG TY CỔ PHẦN TẬP ĐOÀN BẢO HIỂM DBV - CHI NHÁNH VŨNG TÀU</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>285 Đường Cách Mạng Tháng Tám, Phường Hòa Hưng, TP Hồ Chí Minh, Việt Nam</t>
+          <t>Số 29K4 Đường Xuân Diệu, Khu Trung Tâm Thương Mại Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K12" s="6"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
+      <c r="L12" s="13" t="n">
+        <v>819222.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>65538.0</v>
+      </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>800000.0</v>
+        <v>884760.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -711,6 +735,955 @@
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>0100150619-006</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN VIỆT NAM - CHI NHÁNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Số 24 Trần Hưng Đạo, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>3342069.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>267366.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>3609435.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>07/11/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>0313882737-002</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY CỔ PHẦN THC SÀI GÒN TẠI TỈNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>565A Nguyễn An Ninh, Phường Thắng Tam, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>943134.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>75451.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1018585.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3501217143</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THIẾT BỊ DỊCH VỤ XA BỜ O.S</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Số 42B đường 30/4, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>1713480.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>137078.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1850558.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>3500831939</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>BƯU ĐIỆN TRUNG TÂM BÀ RỊA-VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Số 408 Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>1646603.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>131728.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1778331.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>3502314319</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KIẾN BIỂN</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>H4, khu Khang Linh, đường 2/9, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>3057087.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>244567.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>3301654.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>08/11/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>3502276046</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ THƯƠNG MẠI XUẤT NHẬP KHẨU DẦU KHÍ PHÚC KHANG</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Số 291/5B Lê Hồng Phong, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>1775950.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>142076.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>1918026.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>09/11/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>3502006064</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ DẦU KHÍ BIỂN ĐÔNG</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Số 167B Nguyễn An Ninh, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>4594126.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>367530.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>4961656.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>09/11/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>3502290876</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN VINA LOGISTICS</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Khu phố Tân Lộc, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>1159310.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>92745.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>1252055.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>0100109120-008</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>CHI CỤC ĐĂNG KIỂM SỐ 9</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>Số 102 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>2976890.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>238151.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>3215041.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>3500513301</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG - THƯƠNG MẠI LANG PHONG</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Số 200 Lý Tự Trọng,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>2292889.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>183431.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>2476320.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>0105402531-017</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM PVI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Số 58A Võ Thị Sáu, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>2037356.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>162988.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>2200344.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>0300816663-008</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH CÔNG TY TNHH NƯỚC GIẢI KHÁT SUNTORY PEPSICO VIỆT NAM TẠI ĐỒNG NAI</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>KCN Long Bình (Amata), Phường Long Bình, Tỉnh Đồng Nai, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>1853076.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>148246.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>2001322.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>10/11/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>0202285936</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN MỘT THÀNH VIÊN -­ TỔNG CÔNG TY BẢO ĐẢM AN TOÀN HÀNG HẢI VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Số 1 lô 11A đường Lê Hồng Phong,Phường Hải An,Thành phố Hải Phòng,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>3645072.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>291606.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>3936678.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDRa/11/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/11/HDDienTuMayTinhTien.xlsx
@@ -1689,6 +1689,367 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>3500815711</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CẤP NƯỚC TÓC TIÊN</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>ấp 6, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>1415144.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>113212.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>1528356.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>12/11/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>3501741445</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CP SẢN XUẤT VÀ CHẾ BIẾN DẦU KHÍ PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>Khu công nghiệp Cái Mép, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>4594322.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>367546.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>4961868.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>0100150619-006</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN ĐẦU TƯ VÀ PHÁT TRIỂN VIỆT NAM - CHI NHÁNH BÀ RỊA VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Số 24 Trần Hưng Đạo, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>2148780.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>171902.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>2320682.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>13/11/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>3502443402</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG VÀ SẢN XUẤT AN HUY</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>165/15A Đường Đô Lương, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>2375083.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>190007.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>2565090.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>14/11/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>ĐẢNG ỦY CÔNG TY CỔ PHẦN DỊCH VỤ VÀ VẬN TẢI BIỂN VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>Số 1, Thống Nhất, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>4465646.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>357252.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>4822898.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>
